--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>LT Immobilier vous propose en exclusivité : Opportunité rare 4 000€/m² pour des murs de boutiques libres. Local commercial idéalement , dans un environnement recherché et dynamique. Nombreuses possibilités : Activité libérale, médicale, atelier de poterie, studio de yoga.. Implanté dans une rue calme à sens unique, ce bien bénéficie d'un emplacement stratégique, à seulement 8 minutes à pied du métro Robespierre (ligne 9), offrant ainsi une excellente accessibilité pour votre clientèle. Ce local commercial, d'une surface d'environ 60 m², 2m90 d'hauteur sous plafond. Il se compose d'un espace principal facilement aménageable selon vos besoins professionnels. Il est complété par une cave saine de 22 m², directement accessible depuis le local, offrant un espace de stockage pratique et fonctionnel. Vous profiterez également d'une agréable cour privative d'environ 20 m², un véritable atout pour créer un espace extérieur, une zone de détente ou un prolongement d'activité. Le local nécessite une rénovation complète, laissant libre cours à votre imagination pour concevoir un espace sur mesure. Une vitrine est à créer, permettant de valoriser votre activité et d'assurer une visibilité optimale. Le rideau métallique électrique, quant à lui, est neuf. À noter : aucune extraction n'est possible, excluant les activités de restauration nécessitant ce type d'installation Merci de nous contacter uniquement si vous disposez du budget nécessaire à la réalisation de des travaux en sus du prix.</t>
+          <t>LT Immobilier vous propose en exclusivité : Opportunité rare 4 000€/m² pour des murs de boutiques libres. Local commercial idéalement , dans un environnement recherché et dynamique. Nombreuses possibilités : Activité libérale, médicale, atelier de poterie, studio de yoga.. Implanté dans une rue calme à sens unique, ce bien bénéficie d'un emplacement stratégique, à seulement 8 minutes à pied du métro Robespierre (ligne 9), offrant ainsi une excellente accessibilité pour votre clientèle. Ce local commercial, d'une surface d'environ 60 m², 2m90 d'hauteur sous plafond. Il se compose d'un espace principal facilement aménageable selon vos besoins professionnels. Il est complété par une cave saine de 22 m², directement accessible depuis le local, offrant un espace de stockage pratique et fonctionnel. Vous profiterez également d'une agréable cour privative d'environ 20 m², un véritable atout pour créer un espace extérieur, une zone de détente ou un prolongement d'activité. Le local nécessite une rénovation complète, laissant libre cours à votre imagination pour concevoir un espace sur mesure. Une vitrine est à créer, permettant de valoriser votre activité et d'assurer une visibilité optimale. Le rideau métallique électrique, quant à lui, est neuf. À noter : aucune extraction n'est possible, excluant les activités de restauration nécessitant ce type d'installation Merci de nous contacter uniquement si vous disposez du budget nécessaire à la réalisation de des travaux en sus du prix. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : www.georisques.gouv.fr</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>LT Immobilier vous propose en exclusivité : Opportunité rare 4 000€/m² pour des murs de boutiques libres. Local commercial idéalement , dans un environnement recherché et dynamique. Nombreuses possibilités : Activité libérale, médicale, atelier de poterie, studio de yoga.. Implanté dans une rue calme à sens unique, ce bien bénéficie d'un emplacement stratégique, à seulement 8 minutes à pied du métro Robespierre (ligne 9), offrant ainsi une excellente accessibilité pour votre clientèle. Ce local commercial, d'une surface d'environ 60 m², 2m90 d'hauteur sous plafond. Il se compose d'un espace principal facilement aménageable selon vos besoins professionnels. Il est complété par une cave saine de 22 m², directement accessible depuis le local, offrant un espace de stockage pratique et fonctionnel. Vous profiterez également d'une agréable cour privative d'environ 20 m², un véritable atout pour créer un espace extérieur, une zone de détente ou un prolongement d'activité. Le local nécessite une rénovation complète, laissant libre cours à votre imagination pour concevoir un espace sur mesure. Une vitrine est à créer, permettant de valoriser votre activité et d'assurer une visibilité optimale. Le rideau métallique électrique, quant à lui, est neuf. À noter : aucune extraction n'est possible, excluant les activités de restauration nécessitant ce type d'installation Merci de nous contacter uniquement si vous disposez du budget nécessaire à la réalisation de des travaux en sus du prix. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : www.georisques.gouv.fr</t>
+          <t>LT Immobilier vous propose en exclusivité : Opportunité rare 4 000€/m² pour des murs de boutiques libres. Local commercial idéalement , dans un environnement recherché et dynamique. Nombreuses possibilités : Activité libérale, médicale, atelier de poterie, studio de yoga.. Implanté dans une rue calme à sens unique, ce bien bénéficie d'un emplacement stratégique, à seulement 8 minutes à pied du métro Robespierre (ligne 9), offrant ainsi une excellente accessibilité pour votre clientèle. Ce local commercial, d'une surface d'environ 60 m², 2m90 d'hauteur sous plafond. Il se compose d'un espace principal facilement aménageable selon vos besoins professionnels. Il est complété par une cave saine de 22 m², directement accessible depuis le local, offrant un espace de stockage pratique et fonctionnel. Vous profiterez également d'une agréable cour privative d'environ 20 m², un véritable atout pour créer un espace extérieur, une zone de détente ou un prolongement d'activité. Le local nécessite une rénovation complète, laissant libre cours à votre imagination pour concevoir un espace sur mesure. Une vitrine est à créer, permettant de valoriser votre activité et d'assurer une visibilité optimale. Le rideau métallique électrique, quant à lui, est neuf. À noter : aucune extraction n'est possible, excluant les activités de restauration nécessitant ce type d'installation Merci de nous contacter uniquement si vous disposez du budget nécessaire à la réalisation de des travaux en sus du prix.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>LT Immobilier vous propose en exclusivité : Opportunité rare 4 000€/m² pour des murs de boutiques libres. Local commercial idéalement , dans un environnement recherché et dynamique. Nombreuses possibilités : Activité libérale, médicale, atelier de poterie, studio de yoga.. Implanté dans une rue calme à sens unique, ce bien bénéficie d'un emplacement stratégique, à seulement 8 minutes à pied du métro Robespierre (ligne 9), offrant ainsi une excellente accessibilité pour votre clientèle. Ce local commercial, d'une surface d'environ 60 m², 2m90 d'hauteur sous plafond. Il se compose d'un espace principal facilement aménageable selon vos besoins professionnels. Il est complété par une cave saine de 22 m², directement accessible depuis le local, offrant un espace de stockage pratique et fonctionnel. Vous profiterez également d'une agréable cour privative d'environ 20 m², un véritable atout pour créer un espace extérieur, une zone de détente ou un prolongement d'activité. Le local nécessite une rénovation complète, laissant libre cours à votre imagination pour concevoir un espace sur mesure. Une vitrine est à créer, permettant de valoriser votre activité et d'assurer une visibilité optimale. Le rideau métallique électrique, quant à lui, est neuf. À noter : aucune extraction n'est possible, excluant les activités de restauration nécessitant ce type d'installation Merci de nous contacter uniquement si vous disposez du budget nécessaire à la réalisation de des travaux en sus du prix.</t>
+          <t>LT Immobilier vous propose en exclusivité : Opportunité rare 4 000€/m² pour des murs de boutiques libres. Local commercial idéalement , dans un environnement recherché et dynamique. Nombreuses possibilités : Activité libérale, médicale, atelier de poterie, studio de yoga.. Implanté dans une rue calme à sens unique, ce bien bénéficie d'un emplacement stratégique, à seulement 8 minutes à pied du métro Robespierre (ligne 9), offrant ainsi une excellente accessibilité pour votre clientèle. Ce local commercial, d'une surface d'environ 60 m², 2m90 d'hauteur sous plafond. Il se compose d'un espace principal facilement aménageable selon vos besoins professionnels. Il est complété par une cave saine de 22 m², directement accessible depuis le local, offrant un espace de stockage pratique et fonctionnel. Vous profiterez également d'une agréable cour privative d'environ 20 m², un véritable atout pour créer un espace extérieur, une zone de détente ou un prolongement d'activité. Le local nécessite une rénovation complète, laissant libre cours à votre imagination pour concevoir un espace sur mesure. Une vitrine est à créer, permettant de valoriser votre activité et d'assurer une visibilité optimale. Le rideau métallique électrique, quant à lui, est neuf. À noter : aucune extraction n'est possible, excluant les activités de restauration nécessitant ce type d'installation Merci de nous contacter uniquement si vous disposez du budget nécessaire à la réalisation de des travaux en sus du prix. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : www.georisques.gouv.fr</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-montreuil-a253f414.xlsx
+++ b/docs/dossiers/dossier-montreuil-a253f414.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
